--- a/Output/Final4/ValidationMetrics.xlsx
+++ b/Output/Final4/ValidationMetrics.xlsx
@@ -467,46 +467,46 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>510</v>
+        <v>315</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0153657580405251</v>
+        <v>0.0152793810917701</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00235595354483486</v>
+        <v>0.0022925377331857</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0233255602542229</v>
+        <v>0.0232266522803817</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00474693482409427</v>
+        <v>0.00464949884765746</v>
       </c>
       <c r="I2" t="n">
-        <v>0.691393390818498</v>
+        <v>0.695528077876257</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0844725565609815</v>
+        <v>0.079342802628467</v>
       </c>
       <c r="K2" t="n">
-        <v>2384.21990636242</v>
+        <v>2384.21990598307</v>
       </c>
       <c r="L2" t="n">
-        <v>16.4227956251262</v>
+        <v>16.4227936382523</v>
       </c>
       <c r="M2" t="n">
-        <v>2335.73278447923</v>
+        <v>2335.73278222763</v>
       </c>
       <c r="N2" t="n">
-        <v>16.489722317957</v>
+        <v>16.489720043898</v>
       </c>
       <c r="O2" t="n">
-        <v>9.17022879760384</v>
+        <v>9.17022821376398</v>
       </c>
       <c r="P2" t="n">
-        <v>0.514450583642223</v>
+        <v>0.514450482719082</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.68438553196837</v>
+        <v>0.687729187478301</v>
       </c>
     </row>
     <row r="3">
@@ -520,46 +520,46 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>510</v>
+        <v>315</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0261998718379409</v>
+        <v>0.0261279090269969</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00325338695610404</v>
+        <v>0.00320174493931282</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0329193283087879</v>
+        <v>0.032867456086214</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00480133958815459</v>
+        <v>0.00497688912010413</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0293638838924409</v>
+        <v>-0.002133586178853</v>
       </c>
       <c r="J3" t="n">
-        <v>0.189471353239069</v>
+        <v>0.197501147146252</v>
       </c>
       <c r="K3" t="n">
-        <v>2398.52854538807</v>
+        <v>2398.52854782598</v>
       </c>
       <c r="L3" t="n">
-        <v>18.6400283549876</v>
+        <v>18.6400204665653</v>
       </c>
       <c r="M3" t="n">
-        <v>2356.44764710988</v>
+        <v>2356.44764832273</v>
       </c>
       <c r="N3" t="n">
-        <v>17.0224061442375</v>
+        <v>17.022398179101</v>
       </c>
       <c r="O3" t="n">
-        <v>10.8980874822943</v>
+        <v>10.8980874433943</v>
       </c>
       <c r="P3" t="n">
-        <v>0.13212117453457</v>
+        <v>0.13212157563096</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.018963792740459</v>
+        <v>-0.0271862623814146</v>
       </c>
     </row>
     <row r="4">
@@ -573,46 +573,46 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>510</v>
+        <v>315</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0413468496033199</v>
+        <v>0.0411259491557797</v>
       </c>
       <c r="F4" t="n">
-        <v>0.011834580675391</v>
+        <v>0.0114007706292809</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0573433554994783</v>
+        <v>0.0571884690164804</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0146480298123881</v>
+        <v>0.0141771790211144</v>
       </c>
       <c r="I4" t="n">
-        <v>0.312752825933565</v>
+        <v>0.317800399735952</v>
       </c>
       <c r="J4" t="n">
-        <v>0.133324325541403</v>
+        <v>0.133588054583213</v>
       </c>
       <c r="K4" t="n">
-        <v>1511.63817053567</v>
+        <v>1511.63817386122</v>
       </c>
       <c r="L4" t="n">
-        <v>704.592516375345</v>
+        <v>704.592538160096</v>
       </c>
       <c r="M4" t="n">
-        <v>3528.71526210062</v>
+        <v>3528.71524798554</v>
       </c>
       <c r="N4" t="n">
-        <v>834.156873275014</v>
+        <v>834.156876230818</v>
       </c>
       <c r="O4" t="n">
-        <v>11.0686690200436</v>
+        <v>11.0686691211721</v>
       </c>
       <c r="P4" t="n">
-        <v>0.962408534039069</v>
+        <v>0.962408717014471</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.293254899591289</v>
+        <v>0.296506948531568</v>
       </c>
     </row>
   </sheetData>
